--- a/docs/Сюжет_диалоги.xlsx
+++ b/docs/Сюжет_диалоги.xlsx
@@ -615,7 +615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Сюжет «Только самое нужное» — таблица реплик</t>
+          <t>Сюжет «Песнь последнего дара» — таблица реплик</t>
         </is>
       </c>
     </row>
